--- a/data/cepea-consulta-milho.reparado.xlsx
+++ b/data/cepea-consulta-milho.reparado.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\filipe.guidastri\Documents\Projetos\painel-controle-commodities\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\filipe.guidastri\Documents\Projetos\acompanhamento-cotacao\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{207A6263-A84B-49CE-AC7A-2D853FB4D40B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3CBEB08F-DFB7-44F3-BF83-9B24C6F368B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5760" yWindow="3396" windowWidth="17280" windowHeight="8964"/>
   </bookViews>

--- a/data/cepea-consulta-milho.reparado.xlsx
+++ b/data/cepea-consulta-milho.reparado.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\filipe.guidastri\Documents\Projetos\acompanhamento-cotacao\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3CBEB08F-DFB7-44F3-BF83-9B24C6F368B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1DD06A17-00B2-4CFD-9696-DE95B8FE585B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5760" yWindow="3396" windowWidth="17280" windowHeight="8964"/>
+    <workbookView xWindow="3240" yWindow="2052" windowWidth="17280" windowHeight="8964"/>
   </bookViews>
   <sheets>
     <sheet name="Plan 1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1223" uniqueCount="1038">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1244" uniqueCount="1052">
   <si>
     <t>Milho | INDICADOR DO MILHO ESALQ/BM&amp;FBOVESPA</t>
   </si>
@@ -3145,6 +3145,48 @@
   </si>
   <si>
     <t>13/08/2025</t>
+  </si>
+  <si>
+    <t>14/08/2025</t>
+  </si>
+  <si>
+    <t>63,37</t>
+  </si>
+  <si>
+    <t>15/08/2025</t>
+  </si>
+  <si>
+    <t>63,26</t>
+  </si>
+  <si>
+    <t>11,72</t>
+  </si>
+  <si>
+    <t>18/08/2025</t>
+  </si>
+  <si>
+    <t>63,33</t>
+  </si>
+  <si>
+    <t>19/08/2025</t>
+  </si>
+  <si>
+    <t>63,83</t>
+  </si>
+  <si>
+    <t>20/08/2025</t>
+  </si>
+  <si>
+    <t>63,87</t>
+  </si>
+  <si>
+    <t>21/08/2025</t>
+  </si>
+  <si>
+    <t>64,03</t>
+  </si>
+  <si>
+    <t>22/08/2025</t>
   </si>
 </sst>
 </file>
@@ -3596,7 +3638,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J409"/>
+  <dimension ref="A1:J416"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.88671875" customWidth="1"/>
@@ -8114,6 +8156,83 @@
       </c>
       <c r="C409" s="3" t="s">
         <v>500</v>
+      </c>
+    </row>
+    <row r="410" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A410" s="3" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B410" s="3" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C410" s="3" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="411" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A411" s="3" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B411" s="3" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C411" s="3" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="412" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A412" s="3" t="s">
+        <v>1043</v>
+      </c>
+      <c r="B412" s="3" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C412" s="3" t="s">
+        <v>1027</v>
+      </c>
+    </row>
+    <row r="413" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A413" s="3" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B413" s="3" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C413" s="3" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="414" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A414" s="3" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B414" s="3" t="s">
+        <v>1048</v>
+      </c>
+      <c r="C414" s="3" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="415" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A415" s="3" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B415" s="3" t="s">
+        <v>1050</v>
+      </c>
+      <c r="C415" s="3" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="416" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A416" s="3" t="s">
+        <v>1051</v>
+      </c>
+      <c r="B416" s="3" t="s">
+        <v>976</v>
+      </c>
+      <c r="C416" s="3" t="s">
+        <v>654</v>
       </c>
     </row>
   </sheetData>

--- a/data/cepea-consulta-milho.reparado.xlsx
+++ b/data/cepea-consulta-milho.reparado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\filipe.guidastri\Documents\Projetos\acompanhamento-cotacao\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1DD06A17-00B2-4CFD-9696-DE95B8FE585B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AF630473-ACC5-4A1E-9C42-A9E4F12C8692}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3240" yWindow="2052" windowWidth="17280" windowHeight="8964"/>
   </bookViews>

--- a/data/cepea-consulta-milho.reparado.xlsx
+++ b/data/cepea-consulta-milho.reparado.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\filipe.guidastri\Documents\Projetos\acompanhamento-cotacao\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AF630473-ACC5-4A1E-9C42-A9E4F12C8692}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3AD229CD-8727-4C42-9298-2D7B0CD8AD51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3240" yWindow="2052" windowWidth="17280" windowHeight="8964"/>
+    <workbookView xWindow="5760" yWindow="3396" windowWidth="17280" windowHeight="8964"/>
   </bookViews>
   <sheets>
     <sheet name="Plan 1" sheetId="1" r:id="rId1"/>

--- a/data/cepea-consulta-milho.reparado.xlsx
+++ b/data/cepea-consulta-milho.reparado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\filipe.guidastri\Documents\Projetos\acompanhamento-cotacao\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3AD229CD-8727-4C42-9298-2D7B0CD8AD51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5CD45D2D-62F4-481A-A55A-752A83E7A3F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5760" yWindow="3396" windowWidth="17280" windowHeight="8964"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1244" uniqueCount="1052">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1256" uniqueCount="1064">
   <si>
     <t>Milho | INDICADOR DO MILHO ESALQ/BM&amp;FBOVESPA</t>
   </si>
@@ -3187,6 +3187,42 @@
   </si>
   <si>
     <t>22/08/2025</t>
+  </si>
+  <si>
+    <t>25/08/2025</t>
+  </si>
+  <si>
+    <t>64,32</t>
+  </si>
+  <si>
+    <t>11,88</t>
+  </si>
+  <si>
+    <t>26/08/2025</t>
+  </si>
+  <si>
+    <t>64,34</t>
+  </si>
+  <si>
+    <t>11,84</t>
+  </si>
+  <si>
+    <t>27/08/2025</t>
+  </si>
+  <si>
+    <t>64,49</t>
+  </si>
+  <si>
+    <t>11,90</t>
+  </si>
+  <si>
+    <t>28/08/2025</t>
+  </si>
+  <si>
+    <t>64,26</t>
+  </si>
+  <si>
+    <t>11,89</t>
   </si>
 </sst>
 </file>
@@ -3638,7 +3674,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J416"/>
+  <dimension ref="A1:J420"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.88671875" customWidth="1"/>
@@ -8233,6 +8269,50 @@
       </c>
       <c r="C416" s="3" t="s">
         <v>654</v>
+      </c>
+    </row>
+    <row r="417" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A417" s="3" t="s">
+        <v>1052</v>
+      </c>
+      <c r="B417" s="3" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C417" s="3" t="s">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="418" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A418" s="3" t="s">
+        <v>1055</v>
+      </c>
+      <c r="B418" s="3" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C418" s="3" t="s">
+        <v>1057</v>
+      </c>
+    </row>
+    <row r="419" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A419" s="3" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B419" s="3" t="s">
+        <v>1059</v>
+      </c>
+      <c r="C419" s="3" t="s">
+        <v>1060</v>
+      </c>
+    </row>
+    <row r="420" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A420" s="3" t="s">
+        <v>1061</v>
+      </c>
+      <c r="B420" s="3" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C420" s="3" t="s">
+        <v>1063</v>
       </c>
     </row>
   </sheetData>
